--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J256-Pays.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J256-Pays.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="467">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240628120000</t>
+    <t>20241122120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-28T12:00:00+01:00</t>
+    <t>2024-11-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -289,6 +289,12 @@
     <t>Royaume-Uni</t>
   </si>
   <si>
+    <t>99133</t>
+  </si>
+  <si>
+    <t>Territoires britanniques en Méditerranée</t>
+  </si>
+  <si>
     <t>99134</t>
   </si>
   <si>
@@ -505,12 +511,24 @@
     <t>Maldives</t>
   </si>
   <si>
+    <t>99230</t>
+  </si>
+  <si>
+    <t>Hong Kong</t>
+  </si>
+  <si>
     <t>99231</t>
   </si>
   <si>
     <t>Indonésie</t>
   </si>
   <si>
+    <t>99232</t>
+  </si>
+  <si>
+    <t>Macao</t>
+  </si>
+  <si>
     <t>99234</t>
   </si>
   <si>
@@ -691,6 +709,18 @@
     <t>Gambie</t>
   </si>
   <si>
+    <t>99306</t>
+  </si>
+  <si>
+    <t>Territoires britanniques de l'océan Atlantique</t>
+  </si>
+  <si>
+    <t>99308</t>
+  </si>
+  <si>
+    <t>Chagos</t>
+  </si>
+  <si>
     <t>99309</t>
   </si>
   <si>
@@ -715,6 +745,12 @@
     <t>République démocratique du Congo</t>
   </si>
   <si>
+    <t>99313</t>
+  </si>
+  <si>
+    <t>Territoires espagnols en Afrique du Nord</t>
+  </si>
+  <si>
     <t>99314</t>
   </si>
   <si>
@@ -745,6 +781,12 @@
     <t>Somalie</t>
   </si>
   <si>
+    <t>99319</t>
+  </si>
+  <si>
+    <t>Territoires portugais de l'océan Atlantique</t>
+  </si>
+  <si>
     <t>99321</t>
   </si>
   <si>
@@ -1129,12 +1171,24 @@
     <t>Vénézuéla</t>
   </si>
   <si>
+    <t>99425</t>
+  </si>
+  <si>
+    <t>Territoires britanniques dans les Antilles et Bermudes</t>
+  </si>
+  <si>
     <t>99426</t>
   </si>
   <si>
     <t>Jamaïque</t>
   </si>
   <si>
+    <t>99427</t>
+  </si>
+  <si>
+    <t>Territoires britanniques dans l'océan Atlantique Sud</t>
+  </si>
+  <si>
     <t>99428</t>
   </si>
   <si>
@@ -1147,6 +1201,24 @@
     <t>Bélize</t>
   </si>
   <si>
+    <t>99430</t>
+  </si>
+  <si>
+    <t>Groenland</t>
+  </si>
+  <si>
+    <t>99431</t>
+  </si>
+  <si>
+    <t>Aruba</t>
+  </si>
+  <si>
+    <t>99432</t>
+  </si>
+  <si>
+    <t>Territoires des États-Unis en Amérique</t>
+  </si>
+  <si>
     <t>99433</t>
   </si>
   <si>
@@ -1207,6 +1279,24 @@
     <t>Saint-Christophe-et-Niévès</t>
   </si>
   <si>
+    <t>99443</t>
+  </si>
+  <si>
+    <t>Bonaire, Saint-Eustache, Saba</t>
+  </si>
+  <si>
+    <t>99444</t>
+  </si>
+  <si>
+    <t>Curaçao</t>
+  </si>
+  <si>
+    <t>99445</t>
+  </si>
+  <si>
+    <t>Saint-Martin (partie néerlandaise)</t>
+  </si>
+  <si>
     <t>99501</t>
   </si>
   <si>
@@ -1217,6 +1307,18 @@
   </si>
   <si>
     <t>Nouvelle-Zélande</t>
+  </si>
+  <si>
+    <t>99503</t>
+  </si>
+  <si>
+    <t>Pitcairn</t>
+  </si>
+  <si>
+    <t>99505</t>
+  </si>
+  <si>
+    <t>Territoires des États-Unis en Océanie</t>
   </si>
   <si>
     <t>99506</t>
@@ -1582,7 +1684,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B202"/>
+  <dimension ref="A1:B219"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -3194,15 +3296,151 @@
         <v>427</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B203" t="s" s="2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B204" t="s" s="2">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="B205" t="s" s="2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B206" t="s" s="2">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B207" t="s" s="2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B208" t="s" s="2">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B209" t="s" s="2">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B210" t="s" s="2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B211" t="s" s="2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B212" t="s" s="2">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B213" t="s" s="2">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B214" t="s" s="2">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B215" t="s" s="2">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B216" t="s" s="2">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B217" t="s" s="2">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B219" t="s" s="2">
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -3229,26 +3467,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>430</v>
+        <v>464</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>431</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>427</v>
+        <v>461</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>427</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>428</v>
+        <v>462</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>432</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
